--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -808,688 +808,688 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9690,0.0109,0.0047,0.0005</t>
-  </si>
-  <si>
-    <t>0.0063,0.0000,0.0000,0.9993</t>
-  </si>
-  <si>
-    <t>0.9990,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0149,0.0006,0.0002,0.9963</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9952,0.0007,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0047,0.0000,0.0000,0.9995</t>
+  </si>
+  <si>
+    <t>0.9973,0.0000,0.0000,0.0020</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.0001,0.9999</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9983,0.0006,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0001</t>
+    <t>0.9989,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9939,0.0003,0.0025,0.0000</t>
+  </si>
+  <si>
+    <t>0.1227,0.0006,0.8720,0.0006</t>
+  </si>
+  <si>
+    <t>0.0413,0.0038,0.9560,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.0001,0.9980,0.0002</t>
+  </si>
+  <si>
+    <t>0.9880,0.0031,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0039,0.9911,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8750,0.0002,0.1478,0.0004</t>
+  </si>
+  <si>
+    <t>0.0544,0.0015,0.9602,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0003,0.9971,0.0007</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0001,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.5165,0.4888,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9075,0.0337,0.0244,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9929,0.0019,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.8106,0.0003,0.2970,0.0001</t>
+  </si>
+  <si>
+    <t>0.4245,0.6335,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.9981,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.0300,0.9846,0.0019</t>
+  </si>
+  <si>
+    <t>0.0025,0.0004,0.9908,0.0048</t>
+  </si>
+  <si>
+    <t>0.0004,0.0041,0.9978,0.0003</t>
+  </si>
+  <si>
+    <t>0.0061,0.0001,0.9933,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0049,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9988,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0016,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0051,0.0005,0.9975</t>
+  </si>
+  <si>
+    <t>0.0004,0.9986,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0022,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.7506,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0029,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9963,0.0009,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,1.0000,0.0010</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0004,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9891,0.9842,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.0101,0.9926,0.0012</t>
+  </si>
+  <si>
+    <t>0.0000,0.9977,0.9871,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.9957,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.9914,0.0004,0.0074,0.0000</t>
+  </si>
+  <si>
+    <t>0.9810,0.0043,0.0053,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0025,0.9993,0.0014</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.9896,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9952,0.9864,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0030,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9806,0.9693,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.1613,0.9837</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0168,0.9989</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9978,0.0716,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9928,0.9880,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9936,0.5640,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9978,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9951,0.8639,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0013,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0007,0.0002,0.0002</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9972,0.0001,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0004,0.9985,0.0002</t>
-  </si>
-  <si>
-    <t>0.1574,0.0115,0.7994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0016,0.0001,0.9978,0.0002</t>
-  </si>
-  <si>
-    <t>0.9896,0.0013,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.9930,0.0012,0.0009</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9711,0.0002,0.0303,0.0001</t>
-  </si>
-  <si>
-    <t>0.0057,0.0025,0.9910,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0001,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.0002,0.9977,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.8962,0.1042,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.4641,0.0409,0.2764,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9971,0.0403,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9951,0.0002,0.0041,0.0001</t>
-  </si>
-  <si>
-    <t>0.8518,0.2199,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0016,0.9976,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0102,0.6458,0.1705,0.0732</t>
-  </si>
-  <si>
-    <t>0.0059,0.0014,0.9848,0.0017</t>
-  </si>
-  <si>
-    <t>0.0004,0.0011,0.9985,0.0002</t>
-  </si>
-  <si>
-    <t>0.0130,0.0002,0.9852,0.0005</t>
-  </si>
-  <si>
-    <t>0.0014,0.0436,0.9919,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.0025,0.0010,0.9969,0.0001</t>
-  </si>
-  <si>
-    <t>0.0021,0.0014,0.0001,0.9982</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0087,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.1156,0.9775,0.0009</t>
-  </si>
-  <si>
-    <t>0.0001,0.0070,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0004,0.9978,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0005,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9984,0.0002,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0020,0.9999,0.0185</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9947,0.0011,0.0011,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.9914,0.9953,0.0000</t>
+    <t>0.9985,0.0005,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9983,0.0010,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0047,0.0006,0.9927,0.0003</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0027,0.9909,0.0060,0.0008</t>
+  </si>
+  <si>
+    <t>0.0039,0.9930,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.6763,0.4208,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.9257,0.0152,0.0239,0.0027</t>
+  </si>
+  <si>
+    <t>0.0061,0.0020,0.9882,0.0014</t>
+  </si>
+  <si>
+    <t>0.0231,0.0139,0.9300,0.0027</t>
+  </si>
+  <si>
+    <t>0.0035,0.0033,0.9892,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.0035,0.0003,0.9994</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.9971,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.9979,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.6074,0.2534,0.0252,0.0014</t>
+  </si>
+  <si>
+    <t>0.8946,0.0779,0.0060,0.0013</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.9639,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9625,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0084,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0001,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9824,0.0012,0.0072,0.0005</t>
+  </si>
+  <si>
+    <t>0.0377,0.0001,0.9823,0.0001</t>
+  </si>
+  <si>
+    <t>0.9909,0.0012,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.0023,0.0001,0.0001,0.9993</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0006,0.9999</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0164,0.9981</t>
+  </si>
+  <si>
+    <t>0.0000,0.9860,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0283,0.9557,0.0037,0.0038</t>
+  </si>
+  <si>
+    <t>0.2220,0.7909,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.9986,0.0001,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9921,0.0003,0.0001,0.0025</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0040,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.9092,0.0001,0.0076,0.0364</t>
+  </si>
+  <si>
+    <t>0.9802,0.0000,0.0033,0.0029</t>
+  </si>
+  <si>
+    <t>0.8523,0.1223,0.0022,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9966,0.0004,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.1733,0.1694,0.1891,0.0009</t>
+  </si>
+  <si>
+    <t>0.9898,0.0011,0.0037,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9970,0.0003,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.9976,0.0004,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9644,0.0434,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9380,0.0436,0.0074,0.0007</t>
+  </si>
+  <si>
+    <t>0.2158,0.7715,0.0069,0.0009</t>
+  </si>
+  <si>
+    <t>0.0059,0.0104,0.9950,0.0009</t>
+  </si>
+  <si>
+    <t>0.9680,0.0452,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9920,0.0029,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0104,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9629,0.0102,0.0141,0.0057</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0071,0.0123,0.9855,0.0012</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0817,0.9950,0.0002</t>
   </si>
   <si>
     <t>0.0000,0.0003,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0003,0.0002,0.9992,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.9909,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.9979,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9815,0.0002,0.0250,0.0000</t>
-  </si>
-  <si>
-    <t>0.6956,0.0021,0.3081,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0008,0.9994,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.9977,0.9954,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9987,0.9913,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0018,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9969,0.9855,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0254,0.9961</t>
-  </si>
-  <si>
-    <t>0.0000,0.0020,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0396,0.9989</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.2064,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9946,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9841,0.9528,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9710,0.9262,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9680,0.9918,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9602,0.9961,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0001</t>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0027,0.0021,0.9928,0.0004</t>
+  </si>
+  <si>
+    <t>0.0212,0.0005,0.9817,0.0006</t>
+  </si>
+  <si>
+    <t>0.0023,0.0016,0.9952,0.0001</t>
+  </si>
+  <si>
+    <t>0.6011,0.1977,0.0217,0.0002</t>
+  </si>
+  <si>
+    <t>0.0029,0.9829,0.0327,0.0007</t>
+  </si>
+  <si>
+    <t>0.0237,0.0149,0.9393,0.0003</t>
+  </si>
+  <si>
+    <t>0.8720,0.0147,0.0194,0.0033</t>
+  </si>
+  <si>
+    <t>0.0056,0.0051,0.9864,0.0009</t>
+  </si>
+  <si>
+    <t>0.0063,0.9893,0.0021,0.0005</t>
+  </si>
+  <si>
+    <t>0.0007,0.9982,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.8153,0.2253,0.0019,0.0003</t>
+  </si>
+  <si>
+    <t>0.8685,0.1864,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.3914,0.7297,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9900,0.0017,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9897,0.0004,0.0048,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.8901,0.0312,0.0161,0.0008</t>
+  </si>
+  <si>
+    <t>0.0345,0.0011,0.9763,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0025,0.9987,0.0010</t>
+  </si>
+  <si>
+    <t>0.0005,0.0066,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.0009,0.9945,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.0032,0.9963,0.0006</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9963,0.0028,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0035,0.9998,0.0008</t>
+  </si>
+  <si>
+    <t>0.0090,0.0699,0.8992,0.0009</t>
+  </si>
+  <si>
+    <t>0.3289,0.0007,0.6719,0.0024</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0013,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.4350,0.9959,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9995,0.0003</t>
+  </si>
+  <si>
+    <t>0.0017,0.0019,0.9965,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.0015,0.9957,0.0004</t>
+  </si>
+  <si>
+    <t>0.9764,0.0005,0.0189,0.0000</t>
+  </si>
+  <si>
+    <t>0.6461,0.0004,0.3829,0.0009</t>
+  </si>
+  <si>
+    <t>0.9921,0.0002,0.0049,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9994,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9989,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0004,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9967,0.0008,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9901,0.0125,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0005,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0083,0.0015,0.9884,0.0004</t>
-  </si>
-  <si>
-    <t>0.9963,0.0000,0.0029,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0003,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.9956,0.0036,0.0003</t>
-  </si>
-  <si>
-    <t>0.0113,0.9842,0.0013,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9213,0.0955,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.3405,0.0202,0.4320,0.0051</t>
-  </si>
-  <si>
-    <t>0.0088,0.0010,0.9895,0.0003</t>
-  </si>
-  <si>
-    <t>0.0065,0.0085,0.9824,0.0007</t>
-  </si>
-  <si>
-    <t>0.0150,0.0041,0.9770,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.0042,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.9938,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0690,0.8837,0.0179,0.0015</t>
-  </si>
-  <si>
-    <t>0.9434,0.0309,0.0044,0.0030</t>
-  </si>
-  <si>
-    <t>0.9986,0.0002,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0002,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9963,0.9975,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9919,0.9975,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0035,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0027,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.7898,0.0010,0.1818,0.0014</t>
-  </si>
-  <si>
-    <t>0.0140,0.0000,0.9919,0.0001</t>
-  </si>
-  <si>
-    <t>0.9831,0.0004,0.0107,0.0001</t>
-  </si>
-  <si>
-    <t>0.0056,0.0000,0.0001,0.9981</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0008,0.9997</t>
-  </si>
-  <si>
-    <t>0.0001,0.9757,0.9803,0.0000</t>
-  </si>
-  <si>
-    <t>0.0136,0.9787,0.0031,0.0023</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.2168,0.7416,0.0083,0.0005</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9667,0.0014,0.0001,0.0099</t>
-  </si>
-  <si>
-    <t>0.0002,0.0412,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.9477,0.0004,0.0124,0.0153</t>
-  </si>
-  <si>
-    <t>0.9909,0.0000,0.0009,0.0048</t>
-  </si>
-  <si>
-    <t>0.4694,0.5331,0.0040,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9973,0.0006,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0132,0.9698,0.0080,0.0017</t>
-  </si>
-  <si>
-    <t>0.9897,0.0015,0.0032,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9967,0.0006,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9935,0.0056,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9445,0.0331,0.0068,0.0007</t>
-  </si>
-  <si>
-    <t>0.3975,0.5692,0.0177,0.0007</t>
-  </si>
-  <si>
-    <t>0.0094,0.0371,0.9897,0.0005</t>
-  </si>
-  <si>
-    <t>0.9889,0.0091,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9945,0.0024,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9809,0.0132,0.0015,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.0168,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9687,0.0060,0.0144,0.0042</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0485,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9995,0.0012</t>
-  </si>
-  <si>
-    <t>0.0005,0.0107,0.9976,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0200,0.0031,0.9691,0.0010</t>
-  </si>
-  <si>
-    <t>0.0047,0.0017,0.9935,0.0003</t>
-  </si>
-  <si>
-    <t>0.0692,0.0011,0.9201,0.0011</t>
-  </si>
-  <si>
-    <t>0.3511,0.0837,0.2102,0.0003</t>
-  </si>
-  <si>
-    <t>0.0023,0.4088,0.8149,0.0005</t>
-  </si>
-  <si>
-    <t>0.0188,0.0007,0.9868,0.0000</t>
-  </si>
-  <si>
-    <t>0.9510,0.0142,0.0041,0.0006</t>
-  </si>
-  <si>
-    <t>0.0527,0.0013,0.9523,0.0002</t>
-  </si>
-  <si>
-    <t>0.0136,0.9843,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0898,0.9057,0.0046,0.0005</t>
-  </si>
-  <si>
-    <t>0.4092,0.6283,0.0023,0.0007</t>
-  </si>
-  <si>
-    <t>0.0703,0.9323,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.9857,0.0020,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.8421,0.0005,0.2421,0.0000</t>
-  </si>
-  <si>
-    <t>0.6659,0.0002,0.2042,0.0046</t>
-  </si>
-  <si>
-    <t>0.9269,0.0003,0.1171,0.0000</t>
-  </si>
-  <si>
-    <t>0.2265,0.0008,0.7894,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0026,0.9979,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.0011,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0010,0.9973,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0102,0.9959,0.0005</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0009,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9972,0.0017,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0014,0.9998,0.0005</t>
-  </si>
-  <si>
-    <t>0.0071,0.6950,0.3763,0.0007</t>
-  </si>
-  <si>
-    <t>0.8301,0.0002,0.1183,0.0037</t>
-  </si>
-  <si>
-    <t>0.0044,0.0000,0.9955,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.3819,0.9973,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9984,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.0028,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0413,0.0003,0.9437,0.0032</t>
-  </si>
-  <si>
-    <t>0.9884,0.0005,0.0056,0.0000</t>
-  </si>
-  <si>
-    <t>0.1345,0.0002,0.8803,0.0013</t>
-  </si>
-  <si>
-    <t>0.9987,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9938,0.0041,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9982,0.0008,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9961,0.0027,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0018,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0111,0.0143,0.9496,0.0025</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0077,0.4458,0.7044,0.0027</t>
-  </si>
-  <si>
-    <t>0.0107,0.0641,0.8814,0.0009</t>
-  </si>
-  <si>
-    <t>0.0017,0.0001,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.4353,0.0002,0.3408,0.0302</t>
-  </si>
-  <si>
-    <t>0.1040,0.0007,0.9027,0.0010</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9985,0.0004</t>
-  </si>
-  <si>
-    <t>0.9634,0.0001,0.0001,0.0812</t>
-  </si>
-  <si>
-    <t>0.0002,0.0051,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.1434,0.0001,0.0002,0.9594</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0002,1.0000</t>
-  </si>
-  <si>
-    <t>0.8449,0.0008,0.0001,0.1568</t>
+    <t>0.9868,0.0124,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9963,0.0029,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.1001,0.9587,0.0007</t>
+  </si>
+  <si>
+    <t>0.0003,0.0040,0.9982,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0059,0.9962,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.5874,0.0004,0.3174,0.0088</t>
+  </si>
+  <si>
+    <t>0.0040,0.0005,0.9936,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.9857,0.0012,0.0030,0.0033</t>
+  </si>
+  <si>
+    <t>0.0023,0.0015,0.0000,0.9992</t>
+  </si>
+  <si>
+    <t>0.0044,0.0001,0.0001,0.9988</t>
+  </si>
+  <si>
+    <t>0.9828,0.0022,0.0009,0.0051</t>
   </si>
 </sst>
 </file>
@@ -1875,7 +1875,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1889,7 +1889,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1903,7 +1903,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1917,7 +1917,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1931,7 +1931,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1945,7 +1945,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1959,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1973,7 +1973,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1987,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2001,7 +2001,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2015,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2029,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2043,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2057,7 +2057,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2071,7 +2071,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2085,7 +2085,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2099,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2113,7 +2113,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2127,7 +2127,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2141,7 +2141,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2155,7 +2155,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2169,7 +2169,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2183,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2197,7 +2197,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2211,7 +2211,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2225,7 +2225,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2239,7 +2239,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2253,7 +2253,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2267,7 +2267,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2281,7 +2281,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2295,7 +2295,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2309,7 +2309,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2323,7 +2323,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2337,7 +2337,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2351,7 +2351,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2362,10 +2362,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2379,7 +2379,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2390,10 +2390,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2407,7 +2407,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2421,7 +2421,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2435,7 +2435,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2449,7 +2449,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2463,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2477,7 +2477,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2491,7 +2491,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2505,7 +2505,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2519,7 +2519,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2533,7 +2533,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2547,7 +2547,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2558,10 +2558,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2575,7 +2575,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2589,7 +2589,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2603,7 +2603,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2617,7 +2617,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2631,7 +2631,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2645,7 +2645,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2659,7 +2659,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2673,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2687,7 +2687,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2715,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2729,7 +2729,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2743,7 +2743,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2757,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2771,7 +2771,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2785,7 +2785,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2799,7 +2799,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2813,7 +2813,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>327</v>
+        <v>286</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2827,7 +2827,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2841,7 +2841,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2855,7 +2855,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2869,7 +2869,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2883,7 +2883,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2897,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2911,7 +2911,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2925,7 +2925,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2939,7 +2939,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2953,7 +2953,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2967,7 +2967,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2981,7 +2981,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2995,7 +2995,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3009,7 +3009,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3023,7 +3023,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3037,7 +3037,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3051,7 +3051,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3065,7 +3065,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3079,7 +3079,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3093,7 +3093,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>273</v>
+        <v>349</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3107,7 +3107,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3121,7 +3121,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3135,7 +3135,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3149,7 +3149,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3163,7 +3163,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3177,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3191,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>353</v>
+        <v>275</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3205,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3219,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3233,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>355</v>
+        <v>272</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3247,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3261,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>271</v>
+        <v>355</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3275,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3289,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3303,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>268</v>
+        <v>355</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3317,7 +3317,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3331,7 +3331,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3345,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3359,7 +3359,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3373,7 +3373,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3387,7 +3387,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3401,7 +3401,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3415,7 +3415,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3429,7 +3429,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>327</v>
+        <v>286</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3443,7 +3443,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>366</v>
+        <v>286</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3555,7 +3555,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>308</v>
+        <v>286</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3569,7 +3569,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>374</v>
+        <v>312</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3583,7 +3583,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3597,7 +3597,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3608,10 +3608,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3625,7 +3625,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3639,7 +3639,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3653,7 +3653,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3667,7 +3667,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>268</v>
+        <v>379</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3709,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>268</v>
+        <v>388</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3821,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3835,7 +3835,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3849,7 +3849,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3863,7 +3863,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3877,7 +3877,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3891,7 +3891,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>340</v>
+        <v>393</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3905,7 +3905,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3919,7 +3919,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3933,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3947,7 +3947,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3961,7 +3961,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>395</v>
+        <v>323</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3975,7 +3975,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3989,7 +3989,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4003,7 +4003,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4017,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>268</v>
+        <v>400</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4031,7 +4031,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4045,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4059,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4070,10 +4070,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4087,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4101,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4112,10 +4112,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4129,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4143,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4157,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4171,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>409</v>
+        <v>320</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4185,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4199,7 +4199,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>411</v>
+        <v>379</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4479,7 +4479,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>289</v>
+        <v>431</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4493,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4507,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4521,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4535,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4549,7 +4549,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4560,10 +4560,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4577,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4591,7 +4591,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4605,7 +4605,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4619,7 +4619,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4633,7 +4633,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4644,10 +4644,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4658,10 +4658,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4675,7 +4675,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4689,7 +4689,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4703,7 +4703,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4717,7 +4717,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4731,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4745,7 +4745,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4759,7 +4759,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4773,7 +4773,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4787,7 +4787,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4801,7 +4801,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4815,7 +4815,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4829,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>381</v>
+        <v>456</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4843,7 +4843,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4857,7 +4857,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4871,7 +4871,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>457</v>
+        <v>273</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4885,7 +4885,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4899,7 +4899,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4913,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>409</v>
+        <v>382</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4927,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4941,7 +4941,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4952,10 +4952,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4966,10 +4966,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D223" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4983,7 +4983,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4997,7 +4997,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5011,7 +5011,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5025,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>325</v>
+        <v>468</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5039,7 +5039,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5053,7 +5053,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>430</v>
+        <v>293</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5067,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5081,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5095,7 +5095,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5106,10 +5106,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5123,7 +5123,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5137,7 +5137,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5151,7 +5151,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>474</v>
+        <v>457</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5165,7 +5165,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5179,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5193,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>409</v>
+        <v>478</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5207,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5221,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5235,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5249,7 +5249,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5263,7 +5263,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>480</v>
+        <v>318</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5277,7 +5277,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5291,7 +5291,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5305,7 +5305,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5319,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5333,7 +5333,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5347,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5361,7 +5361,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5375,7 +5375,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5389,7 +5389,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5403,7 +5403,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>490</v>
+        <v>339</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5417,7 +5417,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="256" spans="1:4">
